--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Wk 08-17-2026" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Wk 08-24-2026" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Wk 08-31-2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Wk 09-07-2026" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -534,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T83"/>
+  <dimension ref="A1:T92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3948,11 +3949,7 @@
           <t>08/31/2026 - 09/06/2026</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
+      <c r="B82" s="10" t="n"/>
       <c r="C82" s="4" t="n">
         <v>924</v>
       </c>
@@ -4038,18 +4035,420 @@
         <v>1118</v>
       </c>
     </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P84" s="4" t="inlineStr"/>
+      <c r="Q84" s="4" t="inlineStr"/>
+      <c r="R84" s="4" t="inlineStr"/>
+      <c r="S84" s="4" t="inlineStr"/>
+      <c r="T84" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr"/>
+      <c r="D85" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J85" s="8" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr"/>
+      <c r="L85" s="8" t="inlineStr"/>
+      <c r="M85" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N85" s="8" t="inlineStr"/>
+      <c r="O85" s="8" t="inlineStr"/>
+      <c r="P85" s="8" t="inlineStr"/>
+      <c r="Q85" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R85" s="8" t="inlineStr"/>
+      <c r="S85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+      <c r="D86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="4" t="inlineStr"/>
+      <c r="O86" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P86" s="4" t="inlineStr"/>
+      <c r="Q86" s="4" t="inlineStr"/>
+      <c r="R86" s="4" t="inlineStr"/>
+      <c r="S86" s="4" t="inlineStr"/>
+      <c r="T86" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr"/>
+      <c r="D87" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E87" s="8" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr"/>
+      <c r="G87" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr"/>
+      <c r="L87" s="8" t="inlineStr"/>
+      <c r="M87" s="8" t="inlineStr"/>
+      <c r="N87" s="8" t="inlineStr"/>
+      <c r="O87" s="8" t="inlineStr"/>
+      <c r="P87" s="8" t="inlineStr"/>
+      <c r="Q87" s="8" t="inlineStr"/>
+      <c r="R87" s="8" t="inlineStr"/>
+      <c r="S87" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T87" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="5" t="inlineStr"/>
+      <c r="D88" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N88" s="5" t="inlineStr"/>
+      <c r="O88" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P88" s="5" t="inlineStr"/>
+      <c r="Q88" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R88" s="5" t="inlineStr"/>
+      <c r="S88" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T88" s="5" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr"/>
+      <c r="D89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L89" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M89" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="N89" s="8" t="inlineStr"/>
+      <c r="O89" s="8" t="inlineStr"/>
+      <c r="P89" s="8" t="inlineStr"/>
+      <c r="Q89" s="8" t="inlineStr"/>
+      <c r="R89" s="8" t="inlineStr"/>
+      <c r="S89" s="8" t="inlineStr"/>
+      <c r="T89" s="5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="4" t="inlineStr"/>
+      <c r="R90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr"/>
+      <c r="D91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="8" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr"/>
+      <c r="L91" s="8" t="inlineStr"/>
+      <c r="M91" s="8" t="inlineStr"/>
+      <c r="N91" s="8" t="inlineStr"/>
+      <c r="O91" s="8" t="inlineStr"/>
+      <c r="P91" s="8" t="inlineStr"/>
+      <c r="Q91" s="8" t="inlineStr"/>
+      <c r="R91" s="8" t="inlineStr"/>
+      <c r="S91" s="8" t="inlineStr"/>
+      <c r="T91" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="5" t="inlineStr"/>
+      <c r="D92" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="N92" s="5" t="inlineStr"/>
+      <c r="O92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="5" t="inlineStr"/>
+      <c r="R92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="26">
+  <mergeCells count="28">
+    <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A88:B88"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A78:B78"/>
     <mergeCell ref="A7:B7"/>
@@ -6875,6 +7274,548 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/07/2026 - 09/13/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -23,6 +23,7 @@
     <sheet name="Wk 08-24-2026" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Wk 08-31-2026" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Wk 09-07-2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Wk 09-14-2026" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -535,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T92"/>
+  <dimension ref="A1:T96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4268,37 +4269,45 @@
       </c>
       <c r="C89" s="8" t="inlineStr"/>
       <c r="D89" s="8" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="F89" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G89" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="H89" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K89" s="8" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L89" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M89" s="8" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="N89" s="8" t="inlineStr"/>
-      <c r="O89" s="8" t="inlineStr"/>
+      <c r="O89" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="P89" s="8" t="inlineStr"/>
       <c r="Q89" s="8" t="inlineStr"/>
-      <c r="R89" s="8" t="inlineStr"/>
+      <c r="R89" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="S89" s="8" t="inlineStr"/>
       <c r="T89" s="5" t="n">
-        <v>47</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
@@ -4314,37 +4323,45 @@
       </c>
       <c r="C90" s="4" t="inlineStr"/>
       <c r="D90" s="4" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N90" s="4" t="inlineStr"/>
       <c r="O90" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P90" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" s="4" t="inlineStr"/>
+      <c r="Q90" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R90" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S90" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
@@ -4355,13 +4372,11 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
+          <t>Michael Petrick</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr"/>
-      <c r="D91" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="D91" s="8" t="inlineStr"/>
       <c r="E91" s="8" t="inlineStr"/>
       <c r="F91" s="8" t="inlineStr"/>
       <c r="G91" s="8" t="inlineStr"/>
@@ -4371,73 +4386,221 @@
       <c r="K91" s="8" t="inlineStr"/>
       <c r="L91" s="8" t="inlineStr"/>
       <c r="M91" s="8" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="8" t="n">
+        <v>163</v>
+      </c>
       <c r="O91" s="8" t="inlineStr"/>
       <c r="P91" s="8" t="inlineStr"/>
       <c r="Q91" s="8" t="inlineStr"/>
       <c r="R91" s="8" t="inlineStr"/>
       <c r="S91" s="8" t="inlineStr"/>
       <c r="T91" s="5" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>687</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr"/>
+      <c r="P92" s="4" t="inlineStr"/>
+      <c r="Q92" s="4" t="inlineStr"/>
+      <c r="R92" s="4" t="inlineStr"/>
+      <c r="S92" s="4" t="inlineStr"/>
+      <c r="T92" s="5" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 09/14/2026 - 09/20/2026</t>
         </is>
       </c>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="5" t="inlineStr"/>
-      <c r="D92" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" s="5" t="n">
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="5" t="n">
+        <v>687</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I93" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L92" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="N92" s="5" t="inlineStr"/>
-      <c r="O92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q92" s="5" t="inlineStr"/>
-      <c r="R92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S92" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" s="5" t="n">
-        <v>60</v>
+      <c r="J93" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T93" s="5" t="n">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+      <c r="D94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr"/>
+      <c r="Q94" s="4" t="inlineStr"/>
+      <c r="R94" s="4" t="inlineStr"/>
+      <c r="S94" s="4" t="inlineStr"/>
+      <c r="T94" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr"/>
+      <c r="D95" s="8" t="inlineStr"/>
+      <c r="E95" s="8" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="inlineStr"/>
+      <c r="M95" s="8" t="inlineStr"/>
+      <c r="N95" s="8" t="inlineStr"/>
+      <c r="O95" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" s="8" t="inlineStr"/>
+      <c r="Q95" s="8" t="inlineStr"/>
+      <c r="R95" s="8" t="inlineStr"/>
+      <c r="S95" s="8" t="inlineStr"/>
+      <c r="T95" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="5" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr"/>
+      <c r="O96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" s="5" t="inlineStr"/>
+      <c r="Q96" s="5" t="inlineStr"/>
+      <c r="R96" s="5" t="inlineStr"/>
+      <c r="S96" s="5" t="inlineStr"/>
+      <c r="T96" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="28">
+  <mergeCells count="30">
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -4462,7 +4625,9 @@
     <mergeCell ref="A77:B77"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
@@ -7816,6 +7981,490 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>687</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/14/2026 - 09/20/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="n">
+        <v>687</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -24,6 +24,7 @@
     <sheet name="Wk 08-31-2026" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Wk 09-07-2026" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Wk 09-14-2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Wk 09-21-2026" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -536,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4404,11 +4405,7 @@
           <t>09/14/2026 - 09/20/2026</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
+      <c r="B92" s="10" t="n"/>
       <c r="C92" s="4" t="n">
         <v>687</v>
       </c>
@@ -4511,25 +4508,43 @@
       </c>
       <c r="C94" s="4" t="inlineStr"/>
       <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr"/>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M94" s="4" t="n">
+        <v>46</v>
+      </c>
       <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="P94" s="4" t="inlineStr"/>
       <c r="Q94" s="4" t="inlineStr"/>
       <c r="R94" s="4" t="inlineStr"/>
       <c r="S94" s="4" t="inlineStr"/>
       <c r="T94" s="5" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
@@ -4540,67 +4555,335 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr"/>
-      <c r="D95" s="8" t="inlineStr"/>
+      <c r="D95" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="E95" s="8" t="inlineStr"/>
       <c r="F95" s="8" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="J95" s="8" t="inlineStr"/>
       <c r="K95" s="8" t="inlineStr"/>
-      <c r="L95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="M95" s="8" t="inlineStr"/>
       <c r="N95" s="8" t="inlineStr"/>
       <c r="O95" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P95" s="8" t="inlineStr"/>
+      <c r="P95" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="Q95" s="8" t="inlineStr"/>
       <c r="R95" s="8" t="inlineStr"/>
       <c r="S95" s="8" t="inlineStr"/>
       <c r="T95" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr"/>
+      <c r="O96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q96" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R96" s="4" t="inlineStr"/>
+      <c r="S96" s="4" t="inlineStr"/>
+      <c r="T96" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr"/>
+      <c r="D97" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="inlineStr"/>
+      <c r="M97" s="8" t="inlineStr"/>
+      <c r="N97" s="8" t="inlineStr"/>
+      <c r="O97" s="8" t="inlineStr"/>
+      <c r="P97" s="8" t="inlineStr"/>
+      <c r="Q97" s="8" t="inlineStr"/>
+      <c r="R97" s="8" t="inlineStr"/>
+      <c r="S97" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 09/21/2026 - 09/27/2026</t>
         </is>
       </c>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
-      <c r="K96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="5" t="inlineStr"/>
-      <c r="M96" s="5" t="inlineStr"/>
-      <c r="N96" s="5" t="inlineStr"/>
-      <c r="O96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P96" s="5" t="inlineStr"/>
-      <c r="Q96" s="5" t="inlineStr"/>
-      <c r="R96" s="5" t="inlineStr"/>
-      <c r="S96" s="5" t="inlineStr"/>
-      <c r="T96" s="5" t="n">
-        <v>2</v>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="5" t="inlineStr"/>
+      <c r="D98" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="M98" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="N98" s="5" t="inlineStr"/>
+      <c r="O98" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P98" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q98" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R98" s="5" t="inlineStr"/>
+      <c r="S98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" s="5" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>09/28/2026 - 10/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr"/>
+      <c r="D99" s="8" t="inlineStr"/>
+      <c r="E99" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K99" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L99" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M99" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N99" s="8" t="inlineStr"/>
+      <c r="O99" s="8" t="inlineStr"/>
+      <c r="P99" s="8" t="inlineStr"/>
+      <c r="Q99" s="8" t="inlineStr"/>
+      <c r="R99" s="8" t="inlineStr"/>
+      <c r="S99" s="8" t="inlineStr"/>
+      <c r="T99" s="5" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>09/28/2026 - 10/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="4" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr"/>
+      <c r="P100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="4" t="inlineStr"/>
+      <c r="R100" s="4" t="inlineStr"/>
+      <c r="S100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T100" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/28/2026 - 10/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="n"/>
+      <c r="C101" s="5" t="inlineStr"/>
+      <c r="D101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N101" s="5" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
+      <c r="P101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" s="5" t="inlineStr"/>
+      <c r="R101" s="5" t="inlineStr"/>
+      <c r="S101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T101" s="5" t="n">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="30">
+  <mergeCells count="32">
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -4609,6 +4892,7 @@
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A98:B98"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A88:B88"/>
@@ -4622,6 +4906,7 @@
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A101:B101"/>
     <mergeCell ref="A77:B77"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A22:B22"/>
@@ -8465,6 +8750,534 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/21/2026 - 09/27/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>09/28/2026 - 10/04/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>09/28/2026 - 10/04/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 09/28/2026 - 10/04/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -25,6 +25,7 @@
     <sheet name="Wk 09-07-2026" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Wk 09-14-2026" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Wk 09-21-2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Wk 10-05-2026" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -537,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4599,11 +4600,7 @@
           <t>09/21/2026 - 09/27/2026</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
+      <c r="B96" s="10" t="n"/>
       <c r="C96" s="4" t="inlineStr"/>
       <c r="D96" s="4" t="inlineStr"/>
       <c r="E96" s="4" t="inlineStr"/>
@@ -4881,9 +4878,239 @@
         <v>103</v>
       </c>
     </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr"/>
+      <c r="J102" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M102" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P102" s="4" t="inlineStr"/>
+      <c r="Q102" s="4" t="inlineStr"/>
+      <c r="R102" s="4" t="inlineStr"/>
+      <c r="S102" s="4" t="inlineStr"/>
+      <c r="T102" s="5" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr"/>
+      <c r="D103" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr"/>
+      <c r="F103" s="8" t="inlineStr"/>
+      <c r="G103" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr"/>
+      <c r="L103" s="8" t="inlineStr"/>
+      <c r="M103" s="8" t="inlineStr"/>
+      <c r="N103" s="8" t="inlineStr"/>
+      <c r="O103" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P103" s="8" t="inlineStr"/>
+      <c r="Q103" s="8" t="inlineStr"/>
+      <c r="R103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" s="8" t="inlineStr"/>
+      <c r="T103" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr"/>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M104" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N104" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O104" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P104" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="4" t="inlineStr"/>
+      <c r="R104" s="4" t="inlineStr"/>
+      <c r="S104" s="4" t="inlineStr"/>
+      <c r="T104" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr"/>
+      <c r="D105" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr"/>
+      <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr"/>
+      <c r="L105" s="8" t="inlineStr"/>
+      <c r="M105" s="8" t="inlineStr"/>
+      <c r="N105" s="8" t="inlineStr"/>
+      <c r="O105" s="8" t="inlineStr"/>
+      <c r="P105" s="8" t="inlineStr"/>
+      <c r="Q105" s="8" t="inlineStr"/>
+      <c r="R105" s="8" t="inlineStr"/>
+      <c r="S105" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="n"/>
+      <c r="C106" s="5" t="inlineStr"/>
+      <c r="D106" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="N106" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O106" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P106" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q106" s="5" t="inlineStr"/>
+      <c r="R106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" s="5" t="n">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="32">
+  <mergeCells count="33">
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -4909,6 +5136,7 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A77:B77"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A106:B106"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A10:B10"/>
@@ -9278,6 +9506,377 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/05/2026 - 10/11/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T106"/>
+  <dimension ref="A1:T109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5108,9 +5108,149 @@
         <v>221</v>
       </c>
     </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr"/>
+      <c r="D107" s="8" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr"/>
+      <c r="F107" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
+      <c r="J107" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K107" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L107" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M107" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N107" s="8" t="inlineStr"/>
+      <c r="O107" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P107" s="8" t="inlineStr"/>
+      <c r="Q107" s="8" t="inlineStr"/>
+      <c r="R107" s="8" t="inlineStr"/>
+      <c r="S107" s="8" t="inlineStr"/>
+      <c r="T107" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
+      <c r="D108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="4" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr"/>
+      <c r="P108" s="4" t="inlineStr"/>
+      <c r="Q108" s="4" t="inlineStr"/>
+      <c r="R108" s="4" t="inlineStr"/>
+      <c r="S108" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="5" t="inlineStr"/>
+      <c r="D109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="5" t="inlineStr"/>
+      <c r="F109" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="N109" s="5" t="inlineStr"/>
+      <c r="O109" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P109" s="5" t="inlineStr"/>
+      <c r="Q109" s="5" t="inlineStr"/>
+      <c r="R109" s="5" t="inlineStr"/>
+      <c r="S109" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" s="5" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -5138,6 +5278,7 @@
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A109:B109"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A93:B93"/>
@@ -9512,7 +9653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9869,8 +10010,149 @@
         <v>221</v>
       </c>
     </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -26,6 +26,7 @@
     <sheet name="Wk 09-14-2026" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Wk 09-21-2026" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Wk 10-05-2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Wk 10-12-2026" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -538,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:T114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5121,37 +5122,43 @@
       </c>
       <c r="C107" s="8" t="inlineStr"/>
       <c r="D107" s="8" t="inlineStr"/>
-      <c r="E107" s="8" t="inlineStr"/>
+      <c r="E107" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F107" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H107" s="8" t="inlineStr"/>
-      <c r="I107" s="8" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I107" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="J107" s="8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K107" s="8" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="L107" s="8" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M107" s="8" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="N107" s="8" t="inlineStr"/>
       <c r="O107" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P107" s="8" t="inlineStr"/>
       <c r="Q107" s="8" t="inlineStr"/>
       <c r="R107" s="8" t="inlineStr"/>
       <c r="S107" s="8" t="inlineStr"/>
       <c r="T107" s="5" t="n">
-        <v>61</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
@@ -5167,18 +5174,18 @@
       </c>
       <c r="C108" s="4" t="inlineStr"/>
       <c r="D108" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="4" t="inlineStr"/>
       <c r="K108" s="4" t="inlineStr"/>
@@ -5187,70 +5194,306 @@
         <v>1</v>
       </c>
       <c r="N108" s="4" t="inlineStr"/>
-      <c r="O108" s="4" t="inlineStr"/>
+      <c r="O108" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="P108" s="4" t="inlineStr"/>
-      <c r="Q108" s="4" t="inlineStr"/>
+      <c r="Q108" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R108" s="4" t="inlineStr"/>
       <c r="S108" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T108" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr"/>
+      <c r="D109" s="8" t="inlineStr"/>
+      <c r="E109" s="8" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
+      <c r="J109" s="8" t="inlineStr"/>
+      <c r="K109" s="8" t="inlineStr"/>
+      <c r="L109" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M109" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="8" t="n">
+        <v>146</v>
+      </c>
+      <c r="O109" s="8" t="inlineStr"/>
+      <c r="P109" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" s="8" t="inlineStr"/>
+      <c r="R109" s="8" t="inlineStr"/>
+      <c r="S109" s="8" t="inlineStr"/>
+      <c r="T109" s="5" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr"/>
+      <c r="P110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R110" s="4" t="inlineStr"/>
+      <c r="S110" s="4" t="inlineStr"/>
+      <c r="T110" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="5" t="inlineStr"/>
+      <c r="D111" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="N111" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="O111" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P111" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q111" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R111" s="5" t="inlineStr"/>
+      <c r="S111" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" s="5" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr"/>
+      <c r="D112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H112" s="4" t="inlineStr"/>
+      <c r="I112" s="4" t="inlineStr"/>
+      <c r="J112" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K112" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N112" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O112" s="4" t="inlineStr"/>
+      <c r="P112" s="4" t="inlineStr"/>
+      <c r="Q112" s="4" t="inlineStr"/>
+      <c r="R112" s="4" t="inlineStr"/>
+      <c r="S112" s="4" t="inlineStr"/>
+      <c r="T112" s="5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr"/>
+      <c r="D113" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="8" t="inlineStr"/>
+      <c r="F113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr"/>
+      <c r="J113" s="8" t="inlineStr"/>
+      <c r="K113" s="8" t="inlineStr"/>
+      <c r="L113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" s="8" t="inlineStr"/>
+      <c r="O113" s="8" t="inlineStr"/>
+      <c r="P113" s="8" t="inlineStr"/>
+      <c r="Q113" s="8" t="inlineStr"/>
+      <c r="R113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T113" s="5" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 10/12/2026 - 10/18/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="n"/>
-      <c r="C109" s="5" t="inlineStr"/>
-      <c r="D109" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="5" t="inlineStr"/>
-      <c r="F109" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I109" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="5" t="n">
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="5" t="inlineStr"/>
+      <c r="D114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H114" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K109" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M109" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="N109" s="5" t="inlineStr"/>
-      <c r="O109" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P109" s="5" t="inlineStr"/>
-      <c r="Q109" s="5" t="inlineStr"/>
-      <c r="R109" s="5" t="inlineStr"/>
-      <c r="S109" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T109" s="5" t="n">
-        <v>79</v>
+      <c r="I114" s="5" t="inlineStr"/>
+      <c r="J114" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N114" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O114" s="5" t="inlineStr"/>
+      <c r="P114" s="5" t="inlineStr"/>
+      <c r="Q114" s="5" t="inlineStr"/>
+      <c r="R114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T114" s="5" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="34">
+  <mergeCells count="36">
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -5282,7 +5525,9 @@
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A111:B111"/>
     <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A114:B114"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
@@ -10699,6 +10944,530 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/12/2026 - 10/18/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -27,6 +27,7 @@
     <sheet name="Wk 09-21-2026" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Wk 10-05-2026" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Wk 10-12-2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Wk 10-19-2026" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -539,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T114"/>
+  <dimension ref="A1:T118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5215,11 +5216,7 @@
           <t>10/12/2026 - 10/18/2026</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
+      <c r="B109" s="10" t="n"/>
       <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="8" t="inlineStr"/>
       <c r="E109" s="8" t="inlineStr"/>
@@ -5357,40 +5354,48 @@
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
-      <c r="D112" s="4" t="inlineStr"/>
+      <c r="D112" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E112" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G112" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J112" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K112" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L112" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H112" s="4" t="inlineStr"/>
-      <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K112" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L112" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M112" s="4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N112" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="O112" s="4" t="inlineStr"/>
+      <c r="O112" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="P112" s="4" t="inlineStr"/>
       <c r="Q112" s="4" t="inlineStr"/>
       <c r="R112" s="4" t="inlineStr"/>
       <c r="S112" s="4" t="inlineStr"/>
       <c r="T112" s="5" t="n">
-        <v>57</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
@@ -5406,15 +5411,19 @@
       </c>
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E113" s="8" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="F113" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G113" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="H113" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I113" s="8" t="inlineStr"/>
       <c r="J113" s="8" t="inlineStr"/>
@@ -5423,77 +5432,239 @@
         <v>1</v>
       </c>
       <c r="M113" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N113" s="8" t="inlineStr"/>
-      <c r="O113" s="8" t="inlineStr"/>
-      <c r="P113" s="8" t="inlineStr"/>
-      <c r="Q113" s="8" t="inlineStr"/>
+      <c r="O113" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="R113" s="8" t="n">
         <v>2</v>
       </c>
       <c r="S113" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T113" s="5" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+      <c r="D114" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M114" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N114" s="4" t="inlineStr"/>
+      <c r="O114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" s="4" t="inlineStr"/>
+      <c r="Q114" s="4" t="inlineStr"/>
+      <c r="R114" s="4" t="inlineStr"/>
+      <c r="S114" s="4" t="inlineStr"/>
+      <c r="T114" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr"/>
+      <c r="D115" s="8" t="inlineStr"/>
+      <c r="E115" s="8" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr"/>
+      <c r="J115" s="8" t="inlineStr"/>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="inlineStr"/>
+      <c r="M115" s="8" t="inlineStr"/>
+      <c r="N115" s="8" t="inlineStr"/>
+      <c r="O115" s="8" t="inlineStr"/>
+      <c r="P115" s="8" t="inlineStr"/>
+      <c r="Q115" s="8" t="inlineStr"/>
+      <c r="R115" s="8" t="inlineStr"/>
+      <c r="S115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 10/19/2026 - 10/25/2026</t>
         </is>
       </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="5" t="inlineStr"/>
-      <c r="D114" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G114" s="5" t="n">
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="5" t="inlineStr"/>
+      <c r="D116" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O116" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q116" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" s="5" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>10/26/2026 - 11/01/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr"/>
+      <c r="D117" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="8" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
+      <c r="J117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="8" t="inlineStr"/>
+      <c r="M117" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H114" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I114" s="5" t="inlineStr"/>
-      <c r="J114" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K114" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="O114" s="5" t="inlineStr"/>
-      <c r="P114" s="5" t="inlineStr"/>
-      <c r="Q114" s="5" t="inlineStr"/>
-      <c r="R114" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S114" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T114" s="5" t="n">
-        <v>75</v>
+      <c r="N117" s="8" t="inlineStr"/>
+      <c r="O117" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P117" s="8" t="inlineStr"/>
+      <c r="Q117" s="8" t="inlineStr"/>
+      <c r="R117" s="8" t="inlineStr"/>
+      <c r="S117" s="8" t="inlineStr"/>
+      <c r="T117" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/26/2026 - 11/01/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="5" t="inlineStr"/>
+      <c r="D118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="5" t="inlineStr"/>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr"/>
+      <c r="K118" s="5" t="inlineStr"/>
+      <c r="L118" s="5" t="inlineStr"/>
+      <c r="M118" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N118" s="5" t="inlineStr"/>
+      <c r="O118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" s="5" t="inlineStr"/>
+      <c r="Q118" s="5" t="inlineStr"/>
+      <c r="R118" s="5" t="inlineStr"/>
+      <c r="S118" s="5" t="inlineStr"/>
+      <c r="T118" s="5" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="36">
+  <mergeCells count="38">
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
@@ -5511,6 +5682,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A118:B118"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A55:B55"/>
@@ -5519,6 +5691,7 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A77:B77"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A116:B116"/>
     <mergeCell ref="A106:B106"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A109:B109"/>
@@ -5527,8 +5700,8 @@
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="A111:B111"/>
     <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11468,6 +11641,468 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/19/2026 - 10/25/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>10/26/2026 - 11/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 10/26/2026 - 11/01/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
